--- a/countries/se-x/2026-2029.xlsx
+++ b/countries/se-x/2026-2029.xlsx
@@ -61813,10 +61813,10 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O435" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U435" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="16">
